--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N88_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N88_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.7566787083184</v>
+        <v>5.32296029010174</v>
       </c>
       <c r="D2" t="n">
-        <v>26.57536453183662</v>
+        <v>4.318496736423452</v>
       </c>
       <c r="E2" t="n">
-        <v>12.80409156583118</v>
+        <v>2.080664879447567</v>
       </c>
       <c r="F2" t="n">
-        <v>12.29812915934299</v>
+        <v>1.998445988393235</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.64126717715213</v>
+        <v>0.7542059162872212</v>
       </c>
       <c r="D3" t="n">
-        <v>4.523856403702543</v>
+        <v>0.7351266656016633</v>
       </c>
       <c r="E3" t="n">
-        <v>12.80409156583118</v>
+        <v>2.080664879447567</v>
       </c>
       <c r="F3" t="n">
-        <v>12.29812915934299</v>
+        <v>1.998445988393235</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.14125920324225</v>
+        <v>6.197954620526866</v>
       </c>
       <c r="D4" t="n">
-        <v>38.04098073013186</v>
+        <v>6.181659368646428</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80409156583118</v>
+        <v>2.080664879447567</v>
       </c>
       <c r="F4" t="n">
-        <v>12.29812915934299</v>
+        <v>1.998445988393235</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.55398994275085</v>
+        <v>4.640023365697013</v>
       </c>
       <c r="D5" t="n">
-        <v>28.77389262540967</v>
+        <v>4.675757551629072</v>
       </c>
       <c r="E5" t="n">
-        <v>12.80409156583118</v>
+        <v>2.080664879447567</v>
       </c>
       <c r="F5" t="n">
-        <v>12.29812915934299</v>
+        <v>1.998445988393235</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
